--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566491471</v>
+        <v>46157.93093235797</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093235797</v>
+        <v>46157.93169838476</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93169838476</v>
+        <v>46157.93398360196</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398360196</v>
+        <v>46157.93716094359</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716094359</v>
+        <v>46158.2821469611</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821469611</v>
+        <v>46158.29676157644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676157644</v>
+        <v>46158.29812809059</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812809059</v>
+        <v>46158.33385682856</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385682856</v>
+        <v>46158.36855440229</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855440229</v>
+        <v>46158.3728618523</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
